--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.75624404729503</v>
+        <v>9.385389657685442</v>
       </c>
       <c r="D2" t="n">
-        <v>58.73828286272526</v>
+        <v>9.544970965192855</v>
       </c>
       <c r="E2" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F2" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.18978641158132</v>
+        <v>7.830840291881965</v>
       </c>
       <c r="D3" t="n">
-        <v>49.16796424542904</v>
+        <v>7.989794189882219</v>
       </c>
       <c r="E3" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F3" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.86360202044651</v>
+        <v>2.415335328322557</v>
       </c>
       <c r="D4" t="n">
-        <v>15.17133312593239</v>
+        <v>2.465341632964013</v>
       </c>
       <c r="E4" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F4" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.60991995611474</v>
+        <v>5.949111992868646</v>
       </c>
       <c r="D5" t="n">
-        <v>34.69845249528802</v>
+        <v>5.638498530484304</v>
       </c>
       <c r="E5" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F5" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.11802046192564</v>
+        <v>1.481678325062917</v>
       </c>
       <c r="D6" t="n">
-        <v>8.759119096611986</v>
+        <v>1.423356853199448</v>
       </c>
       <c r="E6" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F6" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.55034789610277</v>
+        <v>3.9894315331167</v>
       </c>
       <c r="D7" t="n">
-        <v>25.25872018213453</v>
+        <v>4.104542029596861</v>
       </c>
       <c r="E7" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F7" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.4006744929435</v>
+        <v>4.777609605103319</v>
       </c>
       <c r="D8" t="n">
-        <v>26.18821058466669</v>
+        <v>4.255584220008337</v>
       </c>
       <c r="E8" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F8" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.347101063093358</v>
+        <v>1.518903922752671</v>
       </c>
       <c r="D9" t="n">
-        <v>10.29023406080753</v>
+        <v>1.672163034881224</v>
       </c>
       <c r="E9" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F9" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.502046629510801</v>
+        <v>1.544082577295505</v>
       </c>
       <c r="D10" t="n">
-        <v>9.949721233468777</v>
+        <v>1.616829700438676</v>
       </c>
       <c r="E10" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F10" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>13.16842266339806</v>
+        <v>2.139868682802185</v>
       </c>
       <c r="D11" t="n">
-        <v>13.37575203575992</v>
+        <v>2.173559705810987</v>
       </c>
       <c r="E11" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F11" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.51663399231315</v>
+        <v>5.771453023750888</v>
       </c>
       <c r="D12" t="n">
-        <v>35.0332174594655</v>
+        <v>5.692897837163144</v>
       </c>
       <c r="E12" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F12" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>8.278233138659258</v>
+        <v>1.34521288503213</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2605934026945781</v>
+        <v>0.04234642793786895</v>
       </c>
       <c r="E13" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F13" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>2.4375</v>
       </c>
       <c r="D14" t="n">
-        <v>12.98079061391959</v>
+        <v>2.109378474761934</v>
       </c>
       <c r="E14" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F14" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.88898280166945</v>
+        <v>3.719459705271285</v>
       </c>
       <c r="D15" t="n">
-        <v>22.13760916150951</v>
+        <v>3.597361488745295</v>
       </c>
       <c r="E15" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F15" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>1.953093085021324</v>
+        <v>0.3173776263159651</v>
       </c>
       <c r="D16" t="n">
-        <v>1.319037510869173</v>
+        <v>0.2143435955162406</v>
       </c>
       <c r="E16" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F16" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>23.37952174327291</v>
+        <v>3.799172283281848</v>
       </c>
       <c r="D17" t="n">
-        <v>22.41504351204549</v>
+        <v>3.642444570707392</v>
       </c>
       <c r="E17" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F17" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35.7822047272304</v>
+        <v>5.814608268174941</v>
       </c>
       <c r="D18" t="n">
-        <v>34.82007332513668</v>
+        <v>5.658261915334712</v>
       </c>
       <c r="E18" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F18" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.6293165929973</v>
+        <v>6.764763946362061</v>
       </c>
       <c r="D19" t="n">
-        <v>40.47838929601819</v>
+        <v>6.577738260602956</v>
       </c>
       <c r="E19" t="n">
-        <v>15.19691333942282</v>
+        <v>2.469498417656209</v>
       </c>
       <c r="F19" t="n">
-        <v>15.77363945384207</v>
+        <v>2.563216411249336</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
